--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1859,6 +1859,328 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-13 12:51</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>environment_ref_desert_ruins_set</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/7Ngbzd8v/desert-ruins-set.png</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>C:\Users\ihsan\Desktop\Antigravity\Projeler\Youtube\output\series\wild-encounter\refs\environments\desert_ruins_set.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-13 12:51</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/3ymg9Q8M/ep08-giant-anaconda.png</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>C:\Users\ihsan\Desktop\Antigravity\Projeler\Youtube\output\series\wild-encounter\refs\props\ep08_giant_anaconda.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-13 12:54</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9e59cc17a0bdd4827e6835f11eaa85c1_1789329212.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>C:\Users\ihsan\Desktop\Antigravity\Projeler\Youtube\output\series\wild-encounter\episodes\ep08\shots\shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>environment_ref_ocean_tank_set</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/1JYnCh6Y/ocean-tank-set.png</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/environments/ocean_tank_set.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/1fCQfHkX/ep09-giant-polar-bear.png</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep09_giant_polar_bear.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/84d7f1c1e3b70ace6bdb16e47657d5a4_1789423402.mp4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep09/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2181,6 +2181,261 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-15 21:38</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>environment_ref_jungle_set</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/4RbS0NDY/jungle-set.png</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/environments/jungle_set.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-15 21:38</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/mrkm7P3w/ep10-giant-owl.png</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep10_giant_owl.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-15 21:42</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-15 23:07</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-16 01:51</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/66c2b8a348a8b35f1a09c94ee14973d1_1789523276.mp4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2436,6 +2436,234 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-17 21:36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/bj0tzgvR/ep11-giant-squid.png</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep11_giant_squid.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-17 21:42</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b13816748ebc6ef975f41138babb483a_0_1789681131.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep11/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:32</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2a633ff72b0b9c52463d51a699cda272_0_1789752690.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep11/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:49</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/bc9b39ebb9a36573cf55ce607d024c64_0_1789753720.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep11/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2664,6 +2664,344 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-19 20:55</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/zV98mY6Q/ep12-giant-rhinoceros-beetle.png</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep12_giant_rhinoceros_beetle.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-19 21:02</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>378.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2c7cb2c0bc6c1e53ee6085c339bc37d7_0_1789851481.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep12/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:18</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>378.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/368e59f698a9088bc9bd2685a479d7e9_0_1789924382.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep12/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:27</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c230aed969f1a4286b91660d48fe1f2c_0_1789925221.mp4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep12/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:28</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/jvhfvfrP/ep13-giant-komodo-dragon.png</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep13_giant_komodo_dragon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:35</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b07da09c8fb006e86fc1090fc5b790f8_0_1789925524.mp4</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep13/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3002,6 +3002,116 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:12</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/3Yp2dSgD/ep14-giant-lion.png</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep14_giant_lion.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:20</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7318a0484a09f1eaf8776bb01a5c47e4_0_1790029220.mp4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep14/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3112,6 +3112,116 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:16</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/NdPsg1zV/ep15-giant-cobra.png</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep15_giant_cobra.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:22</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/49823db7b001251beb0f6d4cd30877b8_0_1790191161.mp4</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep15/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3222,6 +3222,116 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:44</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/JjCXwRXg/ep16-giant-wasp.png</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep16_giant_wasp.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b17dd0ad4d7e5781338136c119525615_0_1790286526.mp4</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep16/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3332,6 +3332,116 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:46</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/HfJ5hvZQ/ep17-giant-shark.png</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep17_giant_shark.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:50</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/123af5ba0c449e1e5e0039a1b5ccf094_0_1790340543.mp4</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep17/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3442,6 +3442,285 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-26 12:14</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/cSpNnym1/ep18-giant-eagle.png</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep18_giant_eagle.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/CpV6jjzM/ep19-giant-grizzly-bear.png</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep19_giant_grizzly_bear.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-28 23:51</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/70765afbde59d2160f7dcb2c1aff92c6_0_1790639431.mp4</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep18/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-29 03:22</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>378.0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cf3a9d34877a19145792b64064217212_0_1790651376.mp4</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep18/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:36</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/510364368f51f242b2ef789f70385beb_0_1790864936.mp4</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep19/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3721,6 +3721,116 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:51</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/q3b3pwtf/ep20-giant-snapping-turtle.png</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep20_giant_snapping_turtle.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-02 14:22</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/84e2fe96522024afe446582bb75bbe3d_0_1790949208.mp4</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep20/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3831,6 +3831,116 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:30</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/ZzhpvmYX/ep21-giant-tarantula.png</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep21_giant_tarantula.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:37</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ea62bb086de3f0b8943fc232660b725e_0_1791030773.mp4</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep21/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3941,6 +3941,175 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-04 13:11</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/j9fNZWnF/ep22-giant-orca.png</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep22_giant_orca.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-04 13:26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>378.0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/34d0224566f792f4754e31c305ca1bc9_0_1791119637.mp4</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep22/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:05</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9a628c45cae4b358e371d32e1f360166_0_1791216087.mp4</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep22/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4110,6 +4110,344 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:11</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/xkFxgYt/ep23-giant-ostrich.png</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep23_giant_ostrich.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:12</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>378.0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d760f004bac04c0c936068a13d7bdf95_0_1791470195.mp4</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep23/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:37</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/274cf607b1c816cd0b9f15aedcdb0359_0_1791555865.mp4</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep23/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:42</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/NnFf52nG/ep24-giant-gorilla.png</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep24_giant_gorilla.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-10 14:13</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>378.0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/becb481f446149e9686e408d80e07e37_0_1791639892.mp4</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep24/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:47</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6a4e8ed42b53f15421c99d9962613dff_0_1791823534.mp4</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep24/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4448,6 +4448,163 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:02</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/v4KJRHNY/ep25-giant-chameleon.png</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep25_giant_chameleon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:06</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep25/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:32</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/831416d1f655937190c25072299772ae_0_1792153712.mp4</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep25/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4605,6 +4605,163 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:36</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/39GwhKVx/ep26-giant-hippopotamus.png</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep26_giant_hippopotamus.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:42</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep26/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-18 12:10</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d5c13283f3bcb9a0f733aa263be1b297_0_1792325141.mp4</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep26/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4762,6 +4762,163 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:39</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/RTKwdLC5/ep27-giant-moray-eel.png</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep27_giant_moray_eel.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:44</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep27/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:51</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e35b6878f7236bc724689c61a3bba490_0_1792500488.mp4</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep27/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4919,6 +4919,116 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:55</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/39H0GtWT/ep28-giant-pelican.png</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep28_giant_pelican.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:06</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/74729a3ab5f8ed0a8702138d5255669c_0_1792587707.mp4</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep28/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5029,6 +5029,175 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:57</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/N6hs2c8j/ep29-giant-centipede.png</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep29_giant_centipede.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:33</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>378.0</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0947983fe101bb4870e8ac879c834021_0_1792674366.mp4</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep29/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:56</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7f37dfd24aebfe78af01ea695e93a22d_0_1792759262.mp4</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep29/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5198,6 +5198,116 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:03</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/C3cjLJRC/ep30-giant-marine-iguana.png</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep30_giant_marine_iguana.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:15</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7bdc6fb74f44fcde8a6a9656f4f14437_0_1792843587.mp4</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep30/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5308,6 +5308,116 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-25 12:35</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/DfxXL6Fg/ep31-giant-walrus.png</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep31_giant_walrus.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-25 12:48</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/42559b4b20da4c6ff0b1bbe0dbb7b5dc_0_1792931852.mp4</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep31/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5418,6 +5418,116 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:19</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/XZkk8XFC/ep32-giant-anglerfish.png</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep32_giant_anglerfish.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:46</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7e7a3a81e420ba69b09387dcb158c796_0_1793024786.mp4</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep32/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/wild-encounter/series_log.xlsx
+++ b/sentinal_ihsan/wild-encounter/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M92"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5528,6 +5528,163 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:11</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>creature_ref</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/fV6mD1nQ/ep33-giant-scorpion.png</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/refs/props/ep33_giant_scorpion.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:22</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep33/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:25</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f106a1a35cab43b9e9153b4de0651bcb_0_1793369453.mp4</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/wild-encounter/episodes/ep33/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
